--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>디퍼런스짐 PT 부천중동점</t>
+          <t>바디채널&amp;히트35 역곡남부점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>differencegym@naver.com</t>
+          <t>bodyyg@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1367-6621</t>
+          <t>0507-1324-4779</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 199</t>
+          <t>경기 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.difference-gym.com/</t>
+          <t>https://blog.naver.com/bodyyg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4uaho</t>
+          <t>https://talk.naver.com/ct/w4o3p9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="Q2" t="n">
-        <v>1483</v>
+        <v>1976</v>
       </c>
       <c r="R2" t="n">
-        <v>1825</v>
+        <v>2388</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1721487881</t>
+          <t>1856530360</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721487881</t>
+          <t>https://m.place.naver.com/place/1856530360</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,39 +662,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>르미핏pt 부천신중동점</t>
+          <t>여성전용 PT 더스토리짐 부천중동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dkfma8133@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ndj790@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jo1216@hanmail.net</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1351-4129</t>
+          <t>0507-1357-5385</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 284</t>
+          <t>경기 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkfma8133</t>
+          <t>https://thestorygym.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,7 +713,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47mq2</t>
+          <t>https://talk.naver.com/ct/wcci5c</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1301</v>
+        <v>421</v>
       </c>
       <c r="Q3" t="n">
-        <v>2182</v>
+        <v>1519</v>
       </c>
       <c r="R3" t="n">
-        <v>3483</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +742,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1863789309</t>
+          <t>36935832</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1863789309</t>
+          <t>https://m.place.naver.com/place/36935832</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +764,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리온짐PT 부천신중동점</t>
+          <t>디퍼런스짐 PT 부천중동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reongymbbc@naver.com</t>
+          <t>differencegym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1359-9775</t>
+          <t>0507-1367-6621</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기 부천시 원미구 길주로 199</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reongymbbc</t>
+          <t>https://www.difference-gym.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +796,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,12 +811,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wjc0</t>
+          <t>https://talk.naver.com/ct/w4uaho</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Q4" t="n">
-        <v>2490</v>
+        <v>1541</v>
       </c>
       <c r="R4" t="n">
-        <v>2829</v>
+        <v>1886</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +840,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1159530654</t>
+          <t>1721487881</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159530654</t>
+          <t>https://m.place.naver.com/place/1721487881</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,48 +862,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용 PT 더스토리��� 부천중동점</t>
+          <t>한조바디짐 헬스&amp;pt 부천본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ndj790@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>jo1216@hanmail.net</t>
-        </is>
-      </c>
+          <t>hanjo63433@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-5385</t>
+          <t>0507-1423-6343</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 237</t>
+          <t>경기 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://thestorygym.co.kr/</t>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcci5c</t>
+          <t>https://talk.naver.com/ct/w4lr1h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>419</v>
+        <v>196</v>
       </c>
       <c r="Q5" t="n">
-        <v>1479</v>
+        <v>306</v>
       </c>
       <c r="R5" t="n">
-        <v>1898</v>
+        <v>502</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>36935832</t>
+          <t>1375235921</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36935832</t>
+          <t>https://m.place.naver.com/place/1375235921</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -960,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>지엠짐 부천중동점</t>
+          <t>리온짐PT 부천신중동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gmgym_1st@naver.com</t>
+          <t>reongymbbc@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-8822</t>
+          <t>0507-1359-9775</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 191 금영프라자 2층 202호</t>
+          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmgym_1st/</t>
+          <t>https://blog.naver.com/reongymbbc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uge8</t>
+          <t>https://talk.naver.com/ct/w5wjc0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="Q6" t="n">
-        <v>779</v>
+        <v>2510</v>
       </c>
       <c r="R6" t="n">
-        <v>1087</v>
+        <v>2850</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,60 +1036,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1868176633</t>
+          <t>1159530654</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868176633</t>
+          <t>https://m.place.naver.com/place/1159530654</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리본필라테스 부천범박점</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reborn_bb@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>hello@rebornpilates.com</t>
-        </is>
-      </c>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1324-8878</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 양지로92번길 9-3</t>
+          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.rebornpilates.com/beombak_studio</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1109,12 +1105,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjp0</t>
+          <t>https://talk.naver.com/ct/w4a8bu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1123,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>287</v>
+        <v>1429</v>
       </c>
       <c r="Q7" t="n">
-        <v>725</v>
+        <v>3009</v>
       </c>
       <c r="R7" t="n">
-        <v>1012</v>
+        <v>4438</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1138,17 +1134,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1986375178</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986375178</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1160,34 +1156,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청년피티 상동점</t>
+          <t>디엠짐 헬스장</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cnpt1212@naver.com</t>
+          <t>ehehehans@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1407-1212</t>
+          <t>032-230-9200</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 송내대로265번길 17</t>
+          <t>경기 부천시 원미구 부천로 120</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://blog.naver.com/ehehehans</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1197,7 +1193,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1207,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tdfl</t>
+          <t>https://talk.naver.com/ct/wc9e55</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1221,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="Q8" t="n">
-        <v>1473</v>
+        <v>525</v>
       </c>
       <c r="R8" t="n">
-        <v>2008</v>
+        <v>1051</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1236,17 +1232,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37578803</t>
+          <t>1830766808</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37578803</t>
+          <t>https://m.place.naver.com/place/1830766808</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1258,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청년피티 중동점</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cnpt_jd@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-1213</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부흥로315번길 58</t>
+          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cnpt_jd</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47rdn</t>
+          <t>https://talk.naver.com/ct/w42rk8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1319,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>411</v>
+        <v>1217</v>
       </c>
       <c r="Q9" t="n">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="R9" t="n">
-        <v>756</v>
+        <v>1510</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1334,17 +1330,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1576345626</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576345626</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1356,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>바디채널 짐그라운드 상동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>bodych_55@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>0507-1358-8868</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 120</t>
+          <t>경기 부천시 원미구 상동로 83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>https://blog.naver.com/bodych_55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1403,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc9e55</t>
+          <t>https://talk.naver.com/ct/w4s18q</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1417,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="Q10" t="n">
-        <v>524</v>
+        <v>3705</v>
       </c>
       <c r="R10" t="n">
-        <v>1048</v>
+        <v>4254</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1432,51 +1428,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>36943245</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/36943245</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1501,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
+          <t>https://talk.naver.com/ct/w46rbk</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1515,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1200</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="n">
-        <v>292</v>
+        <v>96</v>
       </c>
       <c r="R11" t="n">
-        <v>1492</v>
+        <v>164</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1530,17 +1526,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 505</t>
+          <t>경기도 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o3p9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>412</v>
       </c>
       <c r="Q2" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="R2" t="n">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -683,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 237</t>
+          <t>경기도 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -708,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcci5c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -730,10 +722,10 @@
         <v>421</v>
       </c>
       <c r="Q3" t="n">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -764,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디퍼런스짐 PT 부천중동점</t>
+          <t>리온짐PT 부천신중동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>differencegym@naver.com</t>
+          <t>reongymbbc@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1367-6621</t>
+          <t>0507-1359-9775</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 199</t>
+          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.difference-gym.com/</t>
+          <t>https://blog.naver.com/reongymbbc</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -796,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -806,17 +798,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4uaho</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -825,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Q4" t="n">
-        <v>1541</v>
+        <v>2510</v>
       </c>
       <c r="R4" t="n">
-        <v>1886</v>
+        <v>2850</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -840,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1721487881</t>
+          <t>1159530654</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721487881</t>
+          <t>https://m.place.naver.com/place/1159530654</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -879,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 110-1</t>
+          <t>경기도 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -904,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lr1h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -926,10 +910,10 @@
         <v>196</v>
       </c>
       <c r="Q5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R5" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -960,39 +944,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리온짐PT 부천신중동점</t>
+          <t>디퍼런스짐 PT 부천중동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>reongymbbc@naver.com</t>
+          <t>differencegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1359-9775</t>
+          <t>0507-1367-6621</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기도 부천시 원미구 길주로 199</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reongymbbc</t>
+          <t>https://www.difference-gym.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1007,12 +991,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wjc0</t>
+          <t>https://talk.naver.com/ct/profile</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q6" t="n">
-        <v>2510</v>
+        <v>1549</v>
       </c>
       <c r="R6" t="n">
-        <v>2850</v>
+        <v>1894</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,51 +1020,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1159530654</t>
+          <t>1721487881</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159530654</t>
+          <t>https://m.place.naver.com/place/1721487881</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 신중동점</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-324-3912</t>
+          <t>0507-1449-8088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1105,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4a8bu</t>
+          <t>https://talk.naver.com/ct/wc32u3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1429</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>3009</v>
+        <v>195</v>
       </c>
       <c r="R7" t="n">
-        <v>4438</v>
+        <v>386</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1463533676</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463533676</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1156,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 120</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1198,14 +1182,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9e55</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1217,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>526</v>
+        <v>1427</v>
       </c>
       <c r="Q8" t="n">
-        <v>525</v>
+        <v>3017</v>
       </c>
       <c r="R8" t="n">
-        <v>1051</v>
+        <v>4444</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1251,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1296,14 +1276,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1315,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="Q9" t="n">
         <v>293</v>
       </c>
       <c r="R9" t="n">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1340,41 +1316,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디채널 짐그라운드 상동점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodych_55@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1358-8868</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 83</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodych_55</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1399,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4s18q</t>
+          <t>https://talk.naver.com/ct/w46rbk</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>549</v>
+        <v>68</v>
       </c>
       <c r="Q10" t="n">
-        <v>3705</v>
+        <v>96</v>
       </c>
       <c r="R10" t="n">
-        <v>4254</v>
+        <v>164</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,51 +1404,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36943245</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36943245</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/theflow2023</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1497,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
+          <t>https://talk.naver.com/ct/w4f90o</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,17 +1483,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,17 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 505</t>
+          <t>경기 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o3p9</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +683,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 237</t>
+          <t>경기 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +708,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcci5c</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -722,10 +730,10 @@
         <v>421</v>
       </c>
       <c r="Q3" t="n">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="R3" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -773,7 +781,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +806,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wjc0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -867,7 +879,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 110-1</t>
+          <t>경기 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +904,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lr1h</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 199</t>
+          <t>경기 부천시 원미구 길주로 199</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -991,7 +1007,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/profile</t>
+          <t>https://talk.naver.com/ct/w4uaho</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1008,10 +1024,10 @@
         <v>345</v>
       </c>
       <c r="Q6" t="n">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="R6" t="n">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1157,7 +1173,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1182,10 +1198,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a8bu</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1200,10 +1220,10 @@
         <v>1427</v>
       </c>
       <c r="Q8" t="n">
-        <v>3017</v>
+        <v>3022</v>
       </c>
       <c r="R8" t="n">
-        <v>4444</v>
+        <v>4449</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1251,7 +1271,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1276,10 +1296,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42rk8</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1421,34 +1445,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1332-4663</t>
+          <t>0507-1364-9609</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theflow2023</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,19 +1487,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1483,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>401</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>207</v>
+        <v>461</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 505</t>
+          <t>경기도 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o3p9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -662,43 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>여성전용 PT 더스토리짐 부천중동점</t>
+          <t>리온짐PT 부천신중동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ndj790@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>jo1216@hanmail.net</t>
-        </is>
-      </c>
+          <t>reongymbbc@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1357-5385</t>
+          <t>0507-1359-9775</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 237</t>
+          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://thestorygym.co.kr/</t>
+          <t>https://blog.naver.com/reongymbbc</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -708,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcci5c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -727,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="Q3" t="n">
-        <v>1523</v>
+        <v>2510</v>
       </c>
       <c r="R3" t="n">
-        <v>1944</v>
+        <v>2850</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -742,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36935832</t>
+          <t>1159530654</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36935832</t>
+          <t>https://m.place.naver.com/place/1159530654</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -764,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리온짐PT 부천신중동점</t>
+          <t>한조바디짐 헬스&amp;pt 부천본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reongymbbc@naver.com</t>
+          <t>hanjo63433@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1359-9775</t>
+          <t>0507-1423-6343</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기도 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reongymbbc</t>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wjc0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -825,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>340</v>
+        <v>196</v>
       </c>
       <c r="Q4" t="n">
-        <v>2510</v>
+        <v>307</v>
       </c>
       <c r="R4" t="n">
-        <v>2850</v>
+        <v>503</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -840,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1159530654</t>
+          <t>1375235921</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159530654</t>
+          <t>https://m.place.naver.com/place/1375235921</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -862,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한조바디짐 헬스&amp;pt 부천본점</t>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hanjo63433@naver.com</t>
+          <t>mediet2025@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1423-6343</t>
+          <t>0507-1487-1261</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 110-1</t>
+          <t>경기도 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lr1h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -923,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>196</v>
+        <v>365</v>
       </c>
       <c r="Q5" t="n">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="R5" t="n">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1375235921</t>
+          <t>35013539</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375235921</t>
+          <t>https://m.place.naver.com/place/35013539</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,29 +940,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디퍼런스짐 PT 부천중동점</t>
+          <t>여성전용 PT 더스토리짐 부천중동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>differencegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>ndj790@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>jo1216@hanmail.net</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1367-6621</t>
+          <t>0507-1357-5385</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 199</t>
+          <t>경기도 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.difference-gym.com/</t>
+          <t>https://thestorygym.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1002,17 +986,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4uaho</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>345</v>
+        <v>421</v>
       </c>
       <c r="Q6" t="n">
-        <v>1553</v>
+        <v>1523</v>
       </c>
       <c r="R6" t="n">
-        <v>1898</v>
+        <v>1944</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1721487881</t>
+          <t>36935832</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721487881</t>
+          <t>https://m.place.naver.com/place/36935832</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1075,7 +1055,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기도 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1100,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc32u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1173,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1198,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a8bu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1220,10 +1192,10 @@
         <v>1427</v>
       </c>
       <c r="Q8" t="n">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="R8" t="n">
-        <v>4449</v>
+        <v>4450</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1271,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1296,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,7 +1337,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기도 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1394,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1416,10 +1380,10 @@
         <v>68</v>
       </c>
       <c r="Q10" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1477,7 +1441,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1487,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -1033,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>191</v>
+        <v>1221</v>
       </c>
       <c r="Q7" t="n">
-        <v>195</v>
+        <v>293</v>
       </c>
       <c r="R7" t="n">
-        <v>386</v>
+        <v>1514</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1127,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 신중동점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-324-3912</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기도 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1427</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>3023</v>
+        <v>97</v>
       </c>
       <c r="R8" t="n">
-        <v>4450</v>
+        <v>165</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1463533676</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463533676</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>0507-1364-9609</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1221</v>
+        <v>401</v>
       </c>
       <c r="Q9" t="n">
-        <v>293</v>
+        <v>60</v>
       </c>
       <c r="R9" t="n">
-        <v>1514</v>
+        <v>461</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/theflow2023</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1362,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f90o</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,17 +1377,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,39 +1413,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>올바로필라테스 역곡점</t>
+          <t>스포애니 역곡역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allbaro07@naver.com</t>
+          <t>spoany95_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1364-9609</t>
+          <t>0507-1397-9618</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 517 6층</t>
+          <t>경기도 부천시 소사구 경인로 527</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allbaropilates_yg</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTEy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,7 +1455,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="R11" t="n">
-        <v>461</v>
+        <v>685</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1038887222</t>
+          <t>1758668626</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038887222</t>
+          <t>https://m.place.naver.com/place/1758668626</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -423,10 +423,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q5" t="n">
         <v>258</v>
       </c>
       <c r="R5" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -948,11 +948,7 @@
           <t>ndj790@naver.com</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>jo1216@hanmail.net</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>0507-1357-5385</t>
@@ -971,17 +967,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1026,41 +1022,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>0507-1449-8088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,10 +1076,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc32u3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1221</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>293</v>
+        <v>195</v>
       </c>
       <c r="R7" t="n">
-        <v>1514</v>
+        <v>386</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 오정구 여월로 72</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>68</v>
+        <v>1427</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>3028</v>
       </c>
       <c r="R8" t="n">
-        <v>165</v>
+        <v>4455</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>올바로필라테스 역곡점</t>
+          <t>디엠짐 헬스장</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allbaro07@naver.com</t>
+          <t>ehehehans@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1364-9609</t>
+          <t>032-230-9200</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 517 6층</t>
+          <t>경기도 부천시 원미구 부천로 120</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allbaropilates_yg</t>
+          <t>https://blog.naver.com/ehehehans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>401</v>
+        <v>526</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>526</v>
       </c>
       <c r="R9" t="n">
-        <v>461</v>
+        <v>1052</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1038887222</t>
+          <t>1830766808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038887222</t>
+          <t>https://m.place.naver.com/place/1830766808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1332-4663</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theflow2023</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>1221</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>293</v>
       </c>
       <c r="R10" t="n">
-        <v>207</v>
+        <v>1514</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 역곡역점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spoany95_@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1397-9618</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 527</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTEy</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,15 +1451,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rbk</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>378</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="n">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="R11" t="n">
-        <v>685</v>
+        <v>165</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1758668626</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758668626</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -423,10 +423,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>412</v>
       </c>
       <c r="Q2" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="R2" t="n">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -948,7 +948,11 @@
           <t>ndj790@naver.com</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>jo1216@hanmail.net</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>0507-1357-5385</t>
@@ -967,17 +971,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1029,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc32u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>191</v>
+        <v>1427</v>
       </c>
       <c r="Q7" t="n">
-        <v>195</v>
+        <v>3029</v>
       </c>
       <c r="R7" t="n">
-        <v>386</v>
+        <v>4456</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 신중동점</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1143,13 +1143,13 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-324-3912</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1427</v>
+        <v>1221</v>
       </c>
       <c r="Q8" t="n">
-        <v>3028</v>
+        <v>293</v>
       </c>
       <c r="R8" t="n">
-        <v>4455</v>
+        <v>1514</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1463533676</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463533676</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로 120</t>
+          <t>경기도 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>526</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>526</v>
+        <v>97</v>
       </c>
       <c r="R9" t="n">
-        <v>1052</v>
+        <v>165</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>0507-1364-9609</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1221</v>
+        <v>401</v>
       </c>
       <c r="Q10" t="n">
-        <v>293</v>
+        <v>60</v>
       </c>
       <c r="R10" t="n">
-        <v>1514</v>
+        <v>461</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1409,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/theflow2023</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
+          <t>https://talk.naver.com/ct/w4f90o</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 505</t>
+          <t>경기 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o3p9</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리온짐PT 부천신중동점</t>
+          <t>한조바디짐 헬스&amp;pt 부천본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>reongymbbc@naver.com</t>
+          <t>hanjo63433@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1359-9775</t>
+          <t>0507-1423-6343</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기도 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reongymbbc</t>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>340</v>
+        <v>196</v>
       </c>
       <c r="Q3" t="n">
-        <v>2510</v>
+        <v>307</v>
       </c>
       <c r="R3" t="n">
-        <v>2850</v>
+        <v>503</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1159530654</t>
+          <t>1375235921</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159530654</t>
+          <t>https://m.place.naver.com/place/1375235921</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한조바디짐 헬스&amp;pt 부천본점</t>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hanjo63433@naver.com</t>
+          <t>mediet2025@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1423-6343</t>
+          <t>0507-1487-1261</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 110-1</t>
+          <t>경기도 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>196</v>
+        <v>365</v>
       </c>
       <c r="Q4" t="n">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="R4" t="n">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1375235921</t>
+          <t>35013539</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375235921</t>
+          <t>https://m.place.naver.com/place/35013539</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>메디어트 그룹운동&amp;1:1PT</t>
+          <t>리온짐PT 부천신중동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mediet2025@naver.com</t>
+          <t>reongymbbc@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1487-1261</t>
+          <t>0507-1359-9775</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>https://blog.naver.com/reongymbbc</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +892,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wjc0</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="Q5" t="n">
-        <v>258</v>
+        <v>2510</v>
       </c>
       <c r="R5" t="n">
-        <v>624</v>
+        <v>2850</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35013539</t>
+          <t>1159530654</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35013539</t>
+          <t>https://m.place.naver.com/place/1159530654</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1038,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 신중동점</t>
+          <t>디엠짐 헬스장</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>ehehehans@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-324-3912</t>
+          <t>032-230-9200</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기 부천시 원미구 부천로 120</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/ehehehans</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,10 +1088,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9e55</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1427</v>
+        <v>526</v>
       </c>
       <c r="Q7" t="n">
-        <v>3029</v>
+        <v>525</v>
       </c>
       <c r="R7" t="n">
-        <v>4456</v>
+        <v>1051</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1463533676</t>
+          <t>1830766808</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463533676</t>
+          <t>https://m.place.naver.com/place/1830766808</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1149,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42rk8</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="Q8" t="n">
         <v>293</v>
       </c>
       <c r="R8" t="n">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1243,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rbk</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 505</t>
+          <t>경기도 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o3p9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q2" t="n">
         <v>1978</v>
       </c>
       <c r="R2" t="n">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -867,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wjc0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -936,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1012,10 +1004,10 @@
         <v>421</v>
       </c>
       <c r="Q6" t="n">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="R6" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,41 +1026,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>0507-1449-8088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 120</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,7 +1085,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc9e55</t>
+          <t>https://talk.naver.com/ct/wc32u3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>526</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>525</v>
+        <v>195</v>
       </c>
       <c r="R7" t="n">
-        <v>1051</v>
+        <v>386</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1114,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1183,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
+          <t>https://talk.naver.com/ct/w46rbk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1223</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="R8" t="n">
-        <v>1516</v>
+        <v>165</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1212,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1364-9609</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1271,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>401</v>
       </c>
       <c r="Q9" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="R9" t="n">
-        <v>165</v>
+        <v>461</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1306,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올바로필라테스 역곡점</t>
+          <t>그레이트짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allbaro07@naver.com</t>
+          <t>great-gym3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-9609</t>
+          <t>0507-1475-0514</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 517 6층</t>
+          <t>경기도 부천시 소사구 소사로 124 3층 그레이트짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allbaropilates_yg</t>
+          <t>https://blog.naver.com/great-gym3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1365,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1397,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>401</v>
+        <v>89</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="R10" t="n">
-        <v>461</v>
+        <v>341</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,51 +1400,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1038887222</t>
+          <t>1444003797</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038887222</t>
+          <t>https://m.place.naver.com/place/1444003797</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>스포애니 역곡역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>spoany95_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1332-4663</t>
+          <t>0507-1397-9618</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기도 부천시 소사구 경인로 527</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theflow2023</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTEy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,19 +1459,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,17 +1475,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>378</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>307</v>
       </c>
       <c r="R11" t="n">
-        <v>207</v>
+        <v>685</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>1758668626</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/1758668626</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 505</t>
+          <t>경기 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o3p9</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q2" t="n">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="R2" t="n">
-        <v>2392</v>
+        <v>2397</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한조바디짐 헬스&amp;pt 부천본점</t>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hanjo63433@naver.com</t>
+          <t>mediet2025@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1423-6343</t>
+          <t>0507-1487-1261</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 110-1</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>196</v>
+        <v>365</v>
       </c>
       <c r="Q3" t="n">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1375235921</t>
+          <t>35013539</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375235921</t>
+          <t>https://m.place.naver.com/place/35013539</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>메디어트 그룹운동&amp;1:1PT</t>
+          <t>한조바디짐 헬스&amp;pt 부천본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mediet2025@naver.com</t>
+          <t>hanjo63433@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1487-1261</t>
+          <t>0507-1423-6343</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lr1h</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>365</v>
+        <v>196</v>
       </c>
       <c r="Q4" t="n">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="R4" t="n">
-        <v>623</v>
+        <v>503</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35013539</t>
+          <t>1375235921</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35013539</t>
+          <t>https://m.place.naver.com/place/1375235921</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wjc0</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 237</t>
+          <t>경기 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +1002,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcci5c</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q6" t="n">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="R6" t="n">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1033,34 +1053,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>디엠짐 헬스장</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>ehehehans@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>032-230-9200</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기 부천시 원미구 부천로 120</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>https://blog.naver.com/ehehehans</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc32u3</t>
+          <t>https://talk.naver.com/ct/wc9e55</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>191</v>
+        <v>525</v>
       </c>
       <c r="Q7" t="n">
-        <v>195</v>
+        <v>526</v>
       </c>
       <c r="R7" t="n">
-        <v>386</v>
+        <v>1051</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1830766808</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1830766808</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1131,34 +1151,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
+          <t>https://talk.naver.com/ct/w42rk8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>68</v>
+        <v>1225</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>293</v>
       </c>
       <c r="R8" t="n">
-        <v>165</v>
+        <v>1518</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1229,34 +1249,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>올바로필라테스 역곡점</t>
+          <t>바디플래너 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allbaro07@naver.com</t>
+          <t>bodyplanner2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1364-9609</t>
+          <t>0507-1353-4708</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 517 6층</t>
+          <t>경기 부천시 오정구 여월로 72</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allbaropilates_yg</t>
+          <t>https://blog.naver.com/bodyplanner2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,15 +1291,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rbk</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1291,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>401</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="R9" t="n">
-        <v>461</v>
+        <v>165</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1038887222</t>
+          <t>1504406955</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038887222</t>
+          <t>https://m.place.naver.com/place/1504406955</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1323,34 +1347,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그레이트짐</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>great-gym3@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1475-0514</t>
+          <t>0507-1364-9609</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 소사로 124 3층 그레이트짐</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/great-gym3</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,7 +1389,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1385,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>89</v>
+        <v>401</v>
       </c>
       <c r="Q10" t="n">
-        <v>252</v>
+        <v>60</v>
       </c>
       <c r="R10" t="n">
-        <v>341</v>
+        <v>461</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1444003797</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444003797</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1417,34 +1441,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 역곡역점</t>
+          <t>아레아필라테스앤피티</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spoany95_@naver.com</t>
+          <t>area8525@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1397-9618</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 527</t>
+          <t>경기 부천시 원미구 평천로 708</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTEy</t>
+          <t>https://blog.naver.com/area8525</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,15 +1479,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ndle</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>378</v>
+        <v>430</v>
       </c>
       <c r="Q11" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1758668626</t>
+          <t>1779301355</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758668626</t>
+          <t>https://m.place.naver.com/place/1779301355</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bodyyg@naver.com</t>
+          <t>daels2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 505</t>
+          <t>경기도 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyyg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 81</t>
+          <t>경기도 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 110-1</t>
+          <t>경기도 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reongymbbc@naver.com</t>
+          <t>reongym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -875,12 +875,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reongymbbc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 237</t>
+          <t>경기도 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1002,14 +1002,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcci5c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1024,10 +1020,10 @@
         <v>422</v>
       </c>
       <c r="Q6" t="n">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="R6" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1046,41 +1042,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>0507-1449-8088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 120</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc9e55</t>
+          <t>https://talk.naver.com/ct/wc32u3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>525</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>526</v>
+        <v>195</v>
       </c>
       <c r="R7" t="n">
-        <v>1051</v>
+        <v>386</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1152,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1167,13 +1163,13 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1198,14 +1194,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1217,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1225</v>
+        <v>1428</v>
       </c>
       <c r="Q8" t="n">
-        <v>293</v>
+        <v>3037</v>
       </c>
       <c r="R8" t="n">
-        <v>1518</v>
+        <v>4465</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1296,14 +1288,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1315,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>1226</v>
       </c>
       <c r="Q9" t="n">
-        <v>97</v>
+        <v>293</v>
       </c>
       <c r="R9" t="n">
-        <v>165</v>
+        <v>1519</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1422,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q11" t="n">
         <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_PT.xlsx
+++ b/naver-place-crawler/results_health/부천_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>daels2@naver.com</t>
+          <t>bodyyg@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 505</t>
+          <t>경기 부천시 소사구 경인로 505</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodyyg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,12 +679,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -777,12 +777,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 경인로 110-1</t>
+          <t>경기 부천시 소사구 경인로 110-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reongym@naver.com</t>
+          <t>reongymbbc@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -875,12 +875,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
+          <t>경기 부천시 원미구 신흥로 256 1층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/reongymbbc</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -977,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 237</t>
+          <t>경기 부천시 원미구 길주로 237</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1002,10 +1002,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcci5c</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1024,10 @@
         <v>422</v>
       </c>
       <c r="Q6" t="n">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="R6" t="n">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1169,7 +1173,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,10 +1198,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a8bu</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1212,10 +1220,10 @@
         <v>1428</v>
       </c>
       <c r="Q8" t="n">
-        <v>3037</v>
+        <v>3040</v>
       </c>
       <c r="R8" t="n">
-        <v>4465</v>
+        <v>4468</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1246,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>디엠짐 헬스장</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>ehehehans@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>032-230-9200</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기 부천시 원미구 부천로 120</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/ehehehans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,10 +1296,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9e55</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1226</v>
+        <v>525</v>
       </c>
       <c r="Q9" t="n">
-        <v>293</v>
+        <v>526</v>
       </c>
       <c r="R9" t="n">
-        <v>1519</v>
+        <v>1051</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1830766808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1830766808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1347,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올바로필라테스 역곡점</t>
+          <t>휘트니스피플 우먼 부천역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allbaro07@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-9609</t>
+          <t>032-613-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 517 6층</t>
+          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allbaropilates_yg</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,15 +1389,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42rk8</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>401</v>
+        <v>1226</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>293</v>
       </c>
       <c r="R10" t="n">
-        <v>461</v>
+        <v>1519</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1038887222</t>
+          <t>1701536337</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038887222</t>
+          <t>https://m.place.naver.com/place/1701536337</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,25 +1450,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아레아필라테스앤피티</t>
+          <t>올바로필라테스 역곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>area8525@naver.com</t>
+          <t>allbaro07@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1364-9609</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 평천로 708</t>
+          <t>경기 부천시 소사구 경인로 517 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/area8525</t>
+          <t>https://www.instagram.com/allbaropilates_yg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,19 +1487,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ndle</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="Q11" t="n">
-        <v>322</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>753</v>
+        <v>461</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1779301355</t>
+          <t>1038887222</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779301355</t>
+          <t>https://m.place.naver.com/place/1038887222</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
